--- a/Projects/DSTW/Split Brain/Split-Brain-Chapter-4.4-Calculations.xlsx
+++ b/Projects/DSTW/Split Brain/Split-Brain-Chapter-4.4-Calculations.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="11_3761EC1B7660F486699A68A81BCF414815A1334D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>

--- a/Projects/DSTW/Split Brain/Split-Brain-Chapter-4.4-Calculations.xlsx
+++ b/Projects/DSTW/Split Brain/Split-Brain-Chapter-4.4-Calculations.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="11_3761EC1B7660F486699A68A81BCF414815A1334D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="3810" yWindow="2865" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
